--- a/Scripts_vjcortesa/data_output/GS2_25-24_sessions/vjcortesa_G2_Income_dist_251007.xlsx
+++ b/Scripts_vjcortesa/data_output/GS2_25-24_sessions/vjcortesa_G2_Income_dist_251007.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/jcortesarevalo_tudelft_nl/Documents/Documents/TUDelft/18_Game Data Analysis/R data analysis BEPs/Scripts_vjcortesa/data_output/GS2_25-24_sessions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F23BDB62960D8129871DA435F6C531E2AF181C93" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F41BDB5-3480-4154-842B-6564D304C6FE}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_F23BDB62960D8129871DA435F6C531E2AF181C93" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F73B5DA6-B56F-445A-9958-A9C45C353147}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,8 +27,22 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">df_income_dist!$A$1:$Z$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">housemeasure!$A$1:$R$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">personalmeasure!$A$1:$V$185</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1216,6 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z121"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1299,7 +1314,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1367,7 +1382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1447,7 +1462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1521,7 +1536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -1595,7 +1610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1675,7 +1690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1983,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -2057,7 +2072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2125,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2199,7 +2214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2270,7 +2285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2421,7 +2436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2489,7 +2504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2569,7 +2584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -2643,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -2717,7 +2732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2791,7 +2806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -2859,7 +2874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -2939,7 +2954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -3019,7 +3034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -3093,7 +3108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -3167,7 +3182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -3235,7 +3250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -3309,7 +3324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -3383,7 +3398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -3537,7 +3552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -3605,7 +3620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -3685,7 +3700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -3765,7 +3780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>26</v>
       </c>
@@ -3845,7 +3860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>26</v>
       </c>
@@ -3925,7 +3940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>26</v>
       </c>
@@ -3993,7 +4008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>26</v>
       </c>
@@ -4067,7 +4082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>26</v>
       </c>
@@ -4141,7 +4156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>26</v>
       </c>
@@ -4215,7 +4230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>26</v>
       </c>
@@ -4289,7 +4304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -4357,7 +4372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -4431,7 +4446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>26</v>
       </c>
@@ -4505,7 +4520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>26</v>
       </c>
@@ -4576,7 +4591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -4647,7 +4662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>26</v>
       </c>
@@ -4715,7 +4730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>26</v>
       </c>
@@ -4786,7 +4801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>26</v>
       </c>
@@ -4860,7 +4875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -5011,7 +5026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>26</v>
       </c>
@@ -5079,7 +5094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -5159,7 +5174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -5239,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -5313,7 +5328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -5387,7 +5402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -5455,7 +5470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -5535,7 +5550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>26</v>
       </c>
@@ -5609,7 +5624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -5689,7 +5704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>26</v>
       </c>
@@ -5763,7 +5778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>26</v>
       </c>
@@ -5831,7 +5846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>26</v>
       </c>
@@ -5905,7 +5920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>26</v>
       </c>
@@ -5979,7 +5994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>26</v>
       </c>
@@ -6053,7 +6068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>26</v>
       </c>
@@ -6127,7 +6142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>26</v>
       </c>
@@ -6195,7 +6210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>26</v>
       </c>
@@ -6275,7 +6290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>26</v>
       </c>
@@ -6355,7 +6370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>26</v>
       </c>
@@ -6429,7 +6444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>26</v>
       </c>
@@ -6503,7 +6518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>26</v>
       </c>
@@ -6571,7 +6586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>26</v>
       </c>
@@ -6645,7 +6660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>26</v>
       </c>
@@ -6719,7 +6734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>26</v>
       </c>
@@ -6873,7 +6888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>26</v>
       </c>
@@ -6941,7 +6956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>26</v>
       </c>
@@ -7012,7 +7027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>26</v>
       </c>
@@ -7083,7 +7098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>26</v>
       </c>
@@ -7234,7 +7249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>26</v>
       </c>
@@ -7302,7 +7317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>26</v>
       </c>
@@ -7382,7 +7397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>26</v>
       </c>
@@ -7456,7 +7471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>26</v>
       </c>
@@ -7536,7 +7551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>26</v>
       </c>
@@ -7610,7 +7625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>26</v>
       </c>
@@ -7678,7 +7693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>26</v>
       </c>
@@ -7758,7 +7773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>26</v>
       </c>
@@ -7838,7 +7853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>26</v>
       </c>
@@ -7912,7 +7927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>26</v>
       </c>
@@ -7986,7 +8001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>26</v>
       </c>
@@ -8054,7 +8069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>26</v>
       </c>
@@ -8125,7 +8140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -8196,7 +8211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>26</v>
       </c>
@@ -8270,7 +8285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>26</v>
       </c>
@@ -8341,7 +8356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>26</v>
       </c>
@@ -8409,7 +8424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>26</v>
       </c>
@@ -8483,7 +8498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>26</v>
       </c>
@@ -8563,7 +8578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>26</v>
       </c>
@@ -8643,7 +8658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>26</v>
       </c>
@@ -8717,7 +8732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>26</v>
       </c>
@@ -8785,7 +8800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>26</v>
       </c>
@@ -8865,7 +8880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>26</v>
       </c>
@@ -8945,7 +8960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>26</v>
       </c>
@@ -9025,7 +9040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>26</v>
       </c>
@@ -9099,7 +9114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>26</v>
       </c>
@@ -9167,7 +9182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>26</v>
       </c>
@@ -9241,7 +9256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>26</v>
       </c>
@@ -9321,7 +9336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>26</v>
       </c>
@@ -9395,7 +9410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>26</v>
       </c>
@@ -9469,7 +9484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>26</v>
       </c>
@@ -9537,7 +9552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>26</v>
       </c>
@@ -9611,7 +9626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>26</v>
       </c>
@@ -9691,7 +9706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>26</v>
       </c>
@@ -9771,7 +9786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>26</v>
       </c>
@@ -9845,7 +9860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>26</v>
       </c>
@@ -9913,7 +9928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>26</v>
       </c>
@@ -9993,7 +10008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>26</v>
       </c>
@@ -10067,7 +10082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>26</v>
       </c>
@@ -10147,7 +10162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>26</v>
       </c>
@@ -10228,7 +10243,20 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z121" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Z121" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="22">
+      <filters>
+        <filter val="-1000"/>
+        <filter val="-14000"/>
+        <filter val="1500"/>
+        <filter val="2250"/>
+        <filter val="-6500"/>
+        <filter val="750"/>
+        <filter val="-8000"/>
+        <filter val="-8625"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -29164,6 +29192,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:V185"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -29238,7 +29267,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>332</v>
       </c>
@@ -29306,7 +29335,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>333</v>
       </c>
@@ -29374,7 +29403,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>380</v>
       </c>
@@ -29442,7 +29471,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>381</v>
       </c>
@@ -29510,7 +29539,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>382</v>
       </c>
@@ -29578,7 +29607,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>426</v>
       </c>
@@ -29646,7 +29675,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>427</v>
       </c>
@@ -29714,7 +29743,7 @@
         <v>3750</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>428</v>
       </c>
@@ -29782,7 +29811,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>466</v>
       </c>
@@ -30258,7 +30287,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>331</v>
       </c>
@@ -30323,7 +30352,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>458</v>
       </c>
@@ -30391,7 +30420,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>459</v>
       </c>
@@ -30459,7 +30488,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>338</v>
       </c>
@@ -30527,7 +30556,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>339</v>
       </c>
@@ -30595,7 +30624,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>370</v>
       </c>
@@ -30663,7 +30692,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>371</v>
       </c>
@@ -30731,7 +30760,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>432</v>
       </c>
@@ -30799,7 +30828,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>433</v>
       </c>
@@ -30867,7 +30896,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>464</v>
       </c>
@@ -30935,7 +30964,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>465</v>
       </c>
@@ -31003,7 +31032,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>327</v>
       </c>
@@ -31071,7 +31100,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>328</v>
       </c>
@@ -31139,7 +31168,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>372</v>
       </c>
@@ -31207,7 +31236,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>373</v>
       </c>
@@ -31275,7 +31304,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>374</v>
       </c>
@@ -31343,7 +31372,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>418</v>
       </c>
@@ -31411,7 +31440,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>419</v>
       </c>
@@ -31479,7 +31508,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>420</v>
       </c>
@@ -31547,7 +31576,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>421</v>
       </c>
@@ -31615,7 +31644,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>460</v>
       </c>
@@ -31683,7 +31712,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>461</v>
       </c>
@@ -31751,7 +31780,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>462</v>
       </c>
@@ -31819,7 +31848,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>463</v>
       </c>
@@ -31887,7 +31916,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>334</v>
       </c>
@@ -31952,7 +31981,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>335</v>
       </c>
@@ -32017,7 +32046,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>336</v>
       </c>
@@ -32082,7 +32111,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>377</v>
       </c>
@@ -32147,7 +32176,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>378</v>
       </c>
@@ -32212,7 +32241,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>379</v>
       </c>
@@ -32277,7 +32306,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>407</v>
       </c>
@@ -32342,7 +32371,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>408</v>
       </c>
@@ -32407,7 +32436,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>409</v>
       </c>
@@ -32472,7 +32501,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>467</v>
       </c>
@@ -32540,7 +32569,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>468</v>
       </c>
@@ -32608,7 +32637,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>337</v>
       </c>
@@ -32676,7 +32705,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>388</v>
       </c>
@@ -32744,7 +32773,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>445</v>
       </c>
@@ -32812,7 +32841,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>498</v>
       </c>
@@ -32880,7 +32909,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>499</v>
       </c>
@@ -32948,7 +32977,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>500</v>
       </c>
@@ -33016,7 +33045,7 @@
         <v>4250</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>501</v>
       </c>
@@ -33084,7 +33113,7 @@
         <v>8500</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>340</v>
       </c>
@@ -33152,7 +33181,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>385</v>
       </c>
@@ -33220,7 +33249,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>386</v>
       </c>
@@ -33285,7 +33314,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>387</v>
       </c>
@@ -33350,7 +33379,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>494</v>
       </c>
@@ -33418,7 +33447,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>495</v>
       </c>
@@ -33486,7 +33515,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>496</v>
       </c>
@@ -33554,7 +33583,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>497</v>
       </c>
@@ -33622,7 +33651,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>344</v>
       </c>
@@ -33690,7 +33719,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>345</v>
       </c>
@@ -33758,7 +33787,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>391</v>
       </c>
@@ -33826,7 +33855,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>392</v>
       </c>
@@ -33894,7 +33923,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>446</v>
       </c>
@@ -33962,7 +33991,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>447</v>
       </c>
@@ -34030,7 +34059,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>448</v>
       </c>
@@ -34098,7 +34127,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>449</v>
       </c>
@@ -34166,7 +34195,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>491</v>
       </c>
@@ -34234,7 +34263,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>492</v>
       </c>
@@ -34302,7 +34331,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>493</v>
       </c>
@@ -34370,7 +34399,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>341</v>
       </c>
@@ -34438,7 +34467,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>342</v>
       </c>
@@ -34506,7 +34535,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>343</v>
       </c>
@@ -34574,7 +34603,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>383</v>
       </c>
@@ -34642,7 +34671,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>384</v>
       </c>
@@ -34710,7 +34739,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>434</v>
       </c>
@@ -34778,7 +34807,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>435</v>
       </c>
@@ -34846,7 +34875,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>436</v>
       </c>
@@ -34914,7 +34943,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>487</v>
       </c>
@@ -34982,7 +35011,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>488</v>
       </c>
@@ -35050,7 +35079,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>489</v>
       </c>
@@ -35118,7 +35147,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>490</v>
       </c>
@@ -35186,7 +35215,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>319</v>
       </c>
@@ -35254,7 +35283,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>482</v>
       </c>
@@ -35322,7 +35351,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>483</v>
       </c>
@@ -35390,7 +35419,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>321</v>
       </c>
@@ -35458,7 +35487,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>322</v>
       </c>
@@ -35526,7 +35555,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>357</v>
       </c>
@@ -35594,7 +35623,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>358</v>
       </c>
@@ -35662,7 +35691,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>414</v>
       </c>
@@ -35730,7 +35759,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>415</v>
       </c>
@@ -35798,7 +35827,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>416</v>
       </c>
@@ -35866,7 +35895,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>417</v>
       </c>
@@ -35934,7 +35963,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>469</v>
       </c>
@@ -36002,7 +36031,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>470</v>
       </c>
@@ -36070,7 +36099,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>471</v>
       </c>
@@ -36138,7 +36167,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>472</v>
       </c>
@@ -36206,7 +36235,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>323</v>
       </c>
@@ -36271,7 +36300,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>361</v>
       </c>
@@ -36336,7 +36365,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>362</v>
       </c>
@@ -36401,7 +36430,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>429</v>
       </c>
@@ -36466,7 +36495,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>430</v>
       </c>
@@ -36531,7 +36560,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>484</v>
       </c>
@@ -36599,7 +36628,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>485</v>
       </c>
@@ -36667,7 +36696,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>486</v>
       </c>
@@ -36735,7 +36764,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>481</v>
       </c>
@@ -36803,7 +36832,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>325</v>
       </c>
@@ -36871,7 +36900,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>326</v>
       </c>
@@ -36939,7 +36968,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>363</v>
       </c>
@@ -37007,7 +37036,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>364</v>
       </c>
@@ -37075,7 +37104,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>365</v>
       </c>
@@ -37143,7 +37172,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>366</v>
       </c>
@@ -37211,7 +37240,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>410</v>
       </c>
@@ -37279,7 +37308,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>411</v>
       </c>
@@ -37347,7 +37376,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>412</v>
       </c>
@@ -37415,7 +37444,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>413</v>
       </c>
@@ -37483,7 +37512,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>477</v>
       </c>
@@ -37551,7 +37580,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>478</v>
       </c>
@@ -37619,7 +37648,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>479</v>
       </c>
@@ -37687,7 +37716,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>480</v>
       </c>
@@ -37755,7 +37784,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>330</v>
       </c>
@@ -37823,7 +37852,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>367</v>
       </c>
@@ -37891,7 +37920,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>368</v>
       </c>
@@ -37959,7 +37988,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>369</v>
       </c>
@@ -38027,7 +38056,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>422</v>
       </c>
@@ -38095,7 +38124,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>423</v>
       </c>
@@ -38163,7 +38192,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>424</v>
       </c>
@@ -38231,7 +38260,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>425</v>
       </c>
@@ -38299,7 +38328,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>473</v>
       </c>
@@ -38367,7 +38396,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>474</v>
       </c>
@@ -38435,7 +38464,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>475</v>
       </c>
@@ -38503,7 +38532,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>476</v>
       </c>
@@ -38571,7 +38600,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>393</v>
       </c>
@@ -38639,7 +38668,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>346</v>
       </c>
@@ -38707,7 +38736,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>347</v>
       </c>
@@ -38775,7 +38804,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>348</v>
       </c>
@@ -38843,7 +38872,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>394</v>
       </c>
@@ -38911,7 +38940,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>395</v>
       </c>
@@ -38979,7 +39008,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>396</v>
       </c>
@@ -39047,7 +39076,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>397</v>
       </c>
@@ -39115,7 +39144,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>450</v>
       </c>
@@ -39183,7 +39212,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>451</v>
       </c>
@@ -39251,7 +39280,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>320</v>
       </c>
@@ -39319,7 +39348,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>356</v>
       </c>
@@ -39387,7 +39416,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>406</v>
       </c>
@@ -39455,7 +39484,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>353</v>
       </c>
@@ -39523,7 +39552,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>354</v>
       </c>
@@ -39591,7 +39620,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>355</v>
       </c>
@@ -39659,7 +39688,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>398</v>
       </c>
@@ -39727,7 +39756,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>399</v>
       </c>
@@ -39795,7 +39824,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>400</v>
       </c>
@@ -39863,7 +39892,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>401</v>
       </c>
@@ -39931,7 +39960,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="160" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>437</v>
       </c>
@@ -39999,7 +40028,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>438</v>
       </c>
@@ -40067,7 +40096,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>439</v>
       </c>
@@ -40135,7 +40164,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>440</v>
       </c>
@@ -40203,7 +40232,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>318</v>
       </c>
@@ -40271,7 +40300,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>359</v>
       </c>
@@ -40339,7 +40368,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>360</v>
       </c>
@@ -40407,7 +40436,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>402</v>
       </c>
@@ -40475,7 +40504,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="168" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>403</v>
       </c>
@@ -40543,7 +40572,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="169" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>404</v>
       </c>
@@ -40611,7 +40640,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>405</v>
       </c>
@@ -40679,7 +40708,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>441</v>
       </c>
@@ -40747,7 +40776,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>442</v>
       </c>
@@ -40815,7 +40844,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>443</v>
       </c>
@@ -40883,7 +40912,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>444</v>
       </c>
@@ -40951,7 +40980,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>324</v>
       </c>
@@ -41019,7 +41048,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>349</v>
       </c>
@@ -41087,7 +41116,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>350</v>
       </c>
@@ -41155,7 +41184,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>351</v>
       </c>
@@ -41223,7 +41252,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>352</v>
       </c>
@@ -41291,7 +41320,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>389</v>
       </c>
@@ -41359,7 +41388,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>390</v>
       </c>
@@ -41427,7 +41456,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>452</v>
       </c>
@@ -41495,7 +41524,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>453</v>
       </c>
@@ -41563,7 +41592,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>454</v>
       </c>
@@ -41631,7 +41660,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>455</v>
       </c>
@@ -41700,6 +41729,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:V185" xr:uid="{00000000-0001-0000-0300-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="t1p2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
